--- a/output/roomself_excel/2144.xlsx
+++ b/output/roomself_excel/2144.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,20 +466,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>325975</v>
+        <v>117760</v>
       </c>
       <c r="D2" t="n">
-        <v>7126</v>
+        <v>2752</v>
       </c>
       <c r="E2" t="n">
-        <v>854</v>
+        <v>395</v>
       </c>
       <c r="F2" t="n">
-        <v>654</v>
+        <v>344</v>
       </c>
     </row>
     <row r="3">
@@ -488,20 +488,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>59660</v>
+        <v>204028</v>
       </c>
       <c r="D3" t="n">
-        <v>2016</v>
+        <v>4966</v>
       </c>
       <c r="E3" t="n">
-        <v>337</v>
+        <v>654</v>
       </c>
       <c r="F3" t="n">
-        <v>211</v>
+        <v>548</v>
       </c>
     </row>
     <row r="4">
@@ -514,16 +514,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>128740</v>
+        <v>77175</v>
       </c>
       <c r="D4" t="n">
-        <v>2896</v>
+        <v>2284</v>
       </c>
       <c r="E4" t="n">
-        <v>410</v>
+        <v>339</v>
       </c>
       <c r="F4" t="n">
-        <v>23</v>
+        <v>268</v>
       </c>
     </row>
     <row r="5">
@@ -532,20 +532,20 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>67703</v>
+        <v>128740</v>
       </c>
       <c r="D5" t="n">
-        <v>3055</v>
+        <v>2896</v>
       </c>
       <c r="E5" t="n">
-        <v>543</v>
+        <v>410</v>
       </c>
       <c r="F5" t="n">
-        <v>220</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6">
@@ -564,10 +564,10 @@
         <v>2900</v>
       </c>
       <c r="E6" t="n">
-        <v>630</v>
+        <v>247</v>
       </c>
       <c r="F6" t="n">
-        <v>310</v>
+        <v>29</v>
       </c>
     </row>
     <row r="7">
@@ -576,20 +576,20 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>117760</v>
+        <v>62489</v>
       </c>
       <c r="D7" t="n">
-        <v>2752</v>
+        <v>2492</v>
       </c>
       <c r="E7" t="n">
-        <v>654</v>
+        <v>374</v>
       </c>
       <c r="F7" t="n">
-        <v>395</v>
+        <v>123</v>
       </c>
     </row>
     <row r="8">
@@ -598,20 +598,20 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>29294</v>
+        <v>14560</v>
       </c>
       <c r="D8" t="n">
-        <v>1416</v>
+        <v>1004</v>
       </c>
       <c r="E8" t="n">
-        <v>200</v>
+        <v>91</v>
       </c>
       <c r="F8" t="n">
-        <v>175</v>
+        <v>24</v>
       </c>
     </row>
     <row r="9">
@@ -620,20 +620,20 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>62489</v>
+        <v>44772</v>
       </c>
       <c r="D9" t="n">
-        <v>2492</v>
+        <v>1748</v>
       </c>
       <c r="E9" t="n">
-        <v>374</v>
+        <v>295</v>
       </c>
       <c r="F9" t="n">
-        <v>134</v>
+        <v>197</v>
       </c>
     </row>
     <row r="10">
@@ -642,20 +642,20 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>14560</v>
+        <v>9100</v>
       </c>
       <c r="D10" t="n">
-        <v>1004</v>
+        <v>764</v>
       </c>
       <c r="E10" t="n">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="F10" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="11">
@@ -664,20 +664,20 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Hallway</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>9100</v>
+        <v>59660</v>
       </c>
       <c r="D11" t="n">
-        <v>764</v>
+        <v>2016</v>
       </c>
       <c r="E11" t="n">
-        <v>100</v>
+        <v>337</v>
       </c>
       <c r="F11" t="n">
-        <v>27</v>
+        <v>211</v>
       </c>
     </row>
     <row r="12">
@@ -700,6 +700,50 @@
       </c>
       <c r="F12" t="n">
         <v>227</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>67703</v>
+      </c>
+      <c r="D13" t="n">
+        <v>3055</v>
+      </c>
+      <c r="E13" t="n">
+        <v>197</v>
+      </c>
+      <c r="F13" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>29294</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1416</v>
+      </c>
+      <c r="E14" t="n">
+        <v>200</v>
+      </c>
+      <c r="F14" t="n">
+        <v>175</v>
       </c>
     </row>
   </sheetData>

--- a/output/roomself_excel/2144.xlsx
+++ b/output/roomself_excel/2144.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:J14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,32 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallLength</t>
+          <t>WallDir_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallWidth</t>
+          <t>ExtWallLength_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_2</t>
         </is>
       </c>
     </row>
@@ -475,11 +495,27 @@
       <c r="D2" t="n">
         <v>2752</v>
       </c>
-      <c r="E2" t="n">
-        <v>395</v>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F2" t="n">
-        <v>344</v>
+        <v>368</v>
+      </c>
+      <c r="G2" t="n">
+        <v>24</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>320</v>
+      </c>
+      <c r="J2" t="n">
+        <v>27</v>
       </c>
     </row>
     <row r="3">
@@ -497,11 +533,27 @@
       <c r="D3" t="n">
         <v>4966</v>
       </c>
-      <c r="E3" t="n">
-        <v>654</v>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F3" t="n">
-        <v>548</v>
+        <v>362</v>
+      </c>
+      <c r="G3" t="n">
+        <v>24</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>619</v>
+      </c>
+      <c r="J3" t="n">
+        <v>24</v>
       </c>
     </row>
     <row r="4">
@@ -519,11 +571,27 @@
       <c r="D4" t="n">
         <v>2284</v>
       </c>
-      <c r="E4" t="n">
-        <v>339</v>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F4" t="n">
-        <v>268</v>
+        <v>233</v>
+      </c>
+      <c r="G4" t="n">
+        <v>24</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>315</v>
+      </c>
+      <c r="J4" t="n">
+        <v>24</v>
       </c>
     </row>
     <row r="5">
@@ -541,11 +609,27 @@
       <c r="D5" t="n">
         <v>2896</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
         <v>410</v>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
         <v>23</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>314</v>
+      </c>
+      <c r="J5" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="6">
@@ -563,10 +647,26 @@
       <c r="D6" t="n">
         <v>2900</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>478</v>
+      </c>
+      <c r="G6" t="n">
+        <v>19</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
         <v>247</v>
       </c>
-      <c r="F6" t="n">
+      <c r="J6" t="n">
         <v>29</v>
       </c>
     </row>
@@ -585,11 +685,27 @@
       <c r="D7" t="n">
         <v>2492</v>
       </c>
-      <c r="E7" t="n">
-        <v>374</v>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F7" t="n">
-        <v>123</v>
+        <v>94</v>
+      </c>
+      <c r="G7" t="n">
+        <v>21</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>353</v>
+      </c>
+      <c r="J7" t="n">
+        <v>29</v>
       </c>
     </row>
     <row r="8">
@@ -607,12 +723,20 @@
       <c r="D8" t="n">
         <v>1004</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
         <v>91</v>
       </c>
-      <c r="F8" t="n">
+      <c r="G8" t="n">
         <v>24</v>
       </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -629,12 +753,20 @@
       <c r="D9" t="n">
         <v>1748</v>
       </c>
-      <c r="E9" t="n">
-        <v>295</v>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F9" t="n">
-        <v>197</v>
-      </c>
+        <v>164</v>
+      </c>
+      <c r="G9" t="n">
+        <v>24</v>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -651,12 +783,20 @@
       <c r="D10" t="n">
         <v>764</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
         <v>100</v>
       </c>
-      <c r="F10" t="n">
+      <c r="G10" t="n">
         <v>27</v>
       </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -673,11 +813,27 @@
       <c r="D11" t="n">
         <v>2016</v>
       </c>
-      <c r="E11" t="n">
-        <v>337</v>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F11" t="n">
-        <v>211</v>
+        <v>190</v>
+      </c>
+      <c r="G11" t="n">
+        <v>23</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>314</v>
+      </c>
+      <c r="J11" t="n">
+        <v>21</v>
       </c>
     </row>
     <row r="12">
@@ -695,11 +851,27 @@
       <c r="D12" t="n">
         <v>1872</v>
       </c>
-      <c r="E12" t="n">
-        <v>293</v>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F12" t="n">
-        <v>227</v>
+        <v>535</v>
+      </c>
+      <c r="G12" t="n">
+        <v>14</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>199</v>
+      </c>
+      <c r="J12" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="13">
@@ -717,12 +889,20 @@
       <c r="D13" t="n">
         <v>3055</v>
       </c>
-      <c r="E13" t="n">
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
         <v>197</v>
       </c>
-      <c r="F13" t="n">
+      <c r="G13" t="n">
         <v>21</v>
       </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -739,12 +919,20 @@
       <c r="D14" t="n">
         <v>1416</v>
       </c>
-      <c r="E14" t="n">
-        <v>200</v>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F14" t="n">
-        <v>175</v>
-      </c>
+        <v>165</v>
+      </c>
+      <c r="G14" t="n">
+        <v>21</v>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/roomself_excel/2144.xlsx
+++ b/output/roomself_excel/2144.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Rooms" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:R14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -479,6 +479,46 @@
           <t>ExtWallWidth_2</t>
         </is>
       </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>OpenType_1</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>OpenDir_1</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>OpenLength_1</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>OpenWidth_1</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>OpenType_2</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>OpenDir_2</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>OpenLength_2</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>OpenWidth_2</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -517,6 +557,26 @@
       <c r="J2" t="n">
         <v>27</v>
       </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="M2" t="n">
+        <v>150</v>
+      </c>
+      <c r="N2" t="n">
+        <v>27</v>
+      </c>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -555,6 +615,38 @@
       <c r="J3" t="n">
         <v>24</v>
       </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="M3" t="n">
+        <v>77</v>
+      </c>
+      <c r="N3" t="n">
+        <v>24</v>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>184</v>
+      </c>
+      <c r="R3" t="n">
+        <v>24</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -593,6 +685,26 @@
       <c r="J4" t="n">
         <v>24</v>
       </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="M4" t="n">
+        <v>153</v>
+      </c>
+      <c r="N4" t="n">
+        <v>24</v>
+      </c>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -631,6 +743,26 @@
       <c r="J5" t="n">
         <v>19</v>
       </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="M5" t="n">
+        <v>185</v>
+      </c>
+      <c r="N5" t="n">
+        <v>23</v>
+      </c>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -669,6 +801,26 @@
       <c r="J6" t="n">
         <v>29</v>
       </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="M6" t="n">
+        <v>154</v>
+      </c>
+      <c r="N6" t="n">
+        <v>29</v>
+      </c>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -707,6 +859,26 @@
       <c r="J7" t="n">
         <v>29</v>
       </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="M7" t="n">
+        <v>121</v>
+      </c>
+      <c r="N7" t="n">
+        <v>29</v>
+      </c>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -737,6 +909,14 @@
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -767,6 +947,14 @@
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -797,6 +985,26 @@
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="M10" t="n">
+        <v>79</v>
+      </c>
+      <c r="N10" t="n">
+        <v>27</v>
+      </c>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -835,6 +1043,26 @@
       <c r="J11" t="n">
         <v>21</v>
       </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="M11" t="n">
+        <v>151</v>
+      </c>
+      <c r="N11" t="n">
+        <v>23</v>
+      </c>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -873,6 +1101,26 @@
       <c r="J12" t="n">
         <v>13</v>
       </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="M12" t="n">
+        <v>85</v>
+      </c>
+      <c r="N12" t="n">
+        <v>14</v>
+      </c>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -903,6 +1151,14 @@
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -933,6 +1189,14 @@
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
